--- a/output/ЧТО_ПРОВЕРИТЬ.xlsx
+++ b/output/ЧТО_ПРОВЕРИТЬ.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>тысяч рублей</t>
+          <t>10 строк: «тысяч рублей», «в процентах к предыдущему году*» … «Рентабельность активов, процентов»</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
@@ -711,20 +711,20 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>в процентах к предыдущему году*</t>
+          <t>15 строк: «Валюта баланса», «внеоборотные активы» … «другие краткосрочные обязательства»</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
@@ -740,20 +740,20 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Сальдо прочих доходов и расходов, тысяч рублей</t>
+          <t>10 строк: «Коэффициент текущей ликвидности (нормальное ограничение 200%)», «Коэффициент обеспеченности собственными оборотными средствами» … «Коэффициент ликвидности (нормальное ограничение 80%)»</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr">
@@ -769,25 +769,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Налог на прибыль (доходы) с учетом прочих платежей (поступлений), тысяч рублей</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 4, 5, 6, 7</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -798,25 +798,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Число прибыльных организаций, единиц</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 4, 5, 6, 7</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -827,25 +827,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Удельный вес прибыльных организаций, в процентах от общего числа организаций</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
@@ -856,25 +856,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Число убыточных организаций, единиц</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 4, 5</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -885,25 +885,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Удельный вес убыточных организаций, в процентах от общего числа организаций</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 4, 5</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
@@ -914,25 +914,25 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Рентабельность проданных товаров, продукции (работ, услуг), процентов</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4, 5</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
@@ -943,25 +943,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Рентабельность активов, процентов</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4, 5</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
@@ -972,25 +972,25 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Валюта баланса</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
@@ -1001,25 +1001,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>внеоборотные активы</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 8</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E13" s="1" t="inlineStr"/>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -1030,25 +1030,25 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>материальные внеоборотные активы (включая основные средства, незавершенные капитальные вложения в основные средства)</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -1059,25 +1059,25 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>нематериальные, финансовые и другие внеоборотные активы</t>
+          <t>Всего</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
@@ -1088,25 +1088,25 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" s="1" t="inlineStr"/>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -1117,25 +1117,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>запасы</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 9</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E17" s="1" t="inlineStr"/>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
@@ -1146,956 +1146,28 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>финансовые и другие оборотные активы (включая дебиторскую задолженность)</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>денежные средства и денежные эквиваленты</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1" t="inlineStr"/>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>Капитал и резервы</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>Долгосрочные обязательства</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>займы и кредиты</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>другие долгосрочные обязательства</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Краткосрочные обязательства</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>кредиторская задолженность</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>другие краткосрочные обязательства</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент текущей ликвидности (нормальное ограничение 200%)</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент обеспеченности собственными оборотными средствами</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент автономии (доля собственных средств в валюте баланса, нормальное ограничение больше либо равно 50%)</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Соотношение заемных и собственных средств (нормативное ограничение меньше либо равно 100%)</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="1" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент маневренности (доля собственных оборотных средств к источнику собственных средств)</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>Доля имущества производственного назначения в валюте баланса</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент обеспеченности собственными материальными оборотными средствами</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>Доля долгосрочных обязательств к источнику собственных средств и долгосрочным обязательствам (долг к капитализации)</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент абсолютной ликвидности (нормальное ограничение 20%)</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент ликвидности (нормальное ограничение 80%)</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 6, 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>4, 5</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>4, 5</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>Всего</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 9</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>оранжевый</t>
         </is>

--- a/output/ЧТО_ПРОВЕРИТЬ.xlsx
+++ b/output/ЧТО_ПРОВЕРИТЬ.xlsx
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -708,7 +708,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>тысяч рублей</t>
+          <t>10 строк: «тысяч рублей», «в процентах к предыдущему году*» … «Рентабельность активов, процентов»</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
@@ -733,20 +733,20 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>в процентах к предыдущему году*</t>
+          <t>15 строк: «Валюта баланса», «внеоборотные активы» … «другие краткосрочные обязательства»</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
@@ -762,20 +762,20 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Сальдо прочих доходов и расходов, тысяч рублей</t>
+          <t>10 строк: «Коэффициент текущей ликвидности (нормальное ограничение 200%)», «Коэффициент обеспеченности собственными оборотными средствами» … «Коэффициент ликвидности (нормальное ограничение 80%)»</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr">
@@ -791,25 +791,25 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Налог на прибыль (доходы) с учетом прочих платежей (поступлений), тысяч рублей</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 4, 5, 6, 7</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -820,25 +820,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Число прибыльных организаций, единиц</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 4, 5, 6, 7</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -849,25 +849,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Удельный вес прибыльных организаций, в процентах от общего числа организаций</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
@@ -878,25 +878,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Число убыточных организаций, единиц</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 4, 5</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -907,25 +907,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Удельный вес убыточных организаций, в процентах от общего числа организаций</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2, 3, 4, 5</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
@@ -936,25 +936,25 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Рентабельность проданных товаров, продукции (работ, услуг), процентов</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4, 5</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
@@ -965,25 +965,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Рентабельность активов, процентов</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4, 5</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
@@ -994,25 +994,25 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Валюта баланса</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
@@ -1023,16 +1023,16 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>внеоборотные активы</t>
+          <t>добыча металлических руд</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>5, 7</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
@@ -1041,7 +1041,7 @@
       <c r="E13" s="1" t="inlineStr"/>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Колонка не узнана: её название в Word не совпало ни с одним показателем Excel — см. лист «3 Названия Word и Excel» и раздел «Частые случаи» инструкции</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -1052,25 +1052,25 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>материальные внеоборотные активы (включая основные средства, незавершенные капитальные вложения в основные средства)</t>
+          <t>добыча прочих полезных ископаемых</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Колонка не узнана: её название в Word не совпало ни с одним показателем Excel — см. лист «3 Названия Word и Excel» и раздел «Частые случаи» инструкции</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -1081,25 +1081,25 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>нематериальные, финансовые и другие внеоборотные активы</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 8</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
@@ -1110,25 +1110,25 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>оборотные активы</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1" t="inlineStr"/>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
@@ -1139,25 +1139,25 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>запасы</t>
+          <t>Всего</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="inlineStr"/>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
@@ -1168,25 +1168,25 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>финансовые и другие оборотные активы (включая дебиторскую задолженность)</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 9</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
@@ -1197,956 +1197,28 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>денежные средства и денежные эквиваленты</t>
+          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>2, 3</t>
+          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E19" s="1" t="inlineStr"/>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
+          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>Капитал и резервы</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>Долгосрочные обязательства</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>займы и кредиты</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>другие долгосрочные обязательства</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Краткосрочные обязательства</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>кредиторская задолженность</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>другие краткосрочные обязательства</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент текущей ликвидности (нормальное ограничение 200%)</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент обеспеченности собственными оборотными средствами</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент автономии (доля собственных средств в валюте баланса, нормальное ограничение больше либо равно 50%)</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Соотношение заемных и собственных средств (нормативное ограничение меньше либо равно 100%)</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="1" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент маневренности (доля собственных оборотных средств к источнику собственных средств)</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>Доля имущества производственного назначения в валюте баланса</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент обеспеченности собственными материальными оборотными средствами</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>Доля долгосрочных обязательств к источнику собственных средств и долгосрочным обязательствам (долг к капитализации)</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент абсолютной ликвидности (нормальное ограничение 20%)</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>Коэффициент ликвидности (нормальное ограничение 80%)</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>2, 3</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>Эту таблицу программа не заполняет (в списке таблиц нет Excel-файла) — заполните вручную</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 6, 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>4, 5</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>4, 5</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>добыча металлических руд</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>5, 7</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>Колонка не узнана: её название в Word не совпало ни с одним показателем Excel — см. лист «3 Названия Word и Excel» и раздел «Частые случаи» инструкции</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>добыча прочих полезных ископаемых</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>Колонка не узнана: её название в Word не совпало ни с одним показателем Excel — см. лист «3 Названия Word и Excel» и раздел «Частые случаи» инструкции</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>Всего</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 9</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>оранжевый</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>деятельность по организации и проведению азартных игр и заключению пари, по организации и проведению лотерей</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>Название строки не узнано — см. лист «3 Названия Word и Excel»</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>оранжевый</t>
         </is>
